--- a/results_task_2/deepseek/2_Y_N_TG_4_oil50.xlsx
+++ b/results_task_2/deepseek/2_Y_N_TG_4_oil50.xlsx
@@ -608,7 +608,7 @@
         <v>4.5</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J3" t="n">
         <v>4.3</v>
@@ -670,7 +670,7 @@
         <v>4.2</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J4" t="n">
         <v>4.6</v>
